--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$107</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="684">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T10:00:28+00:00</t>
+    <t>2025-07-07T12:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,6 +691,22 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -2453,7 +2469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP106"/>
+  <dimension ref="A1:AP107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.96875" customWidth="true" bestFit="true"/>
@@ -5026,43 +5042,41 @@
         <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -5110,7 +5124,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5134,7 +5148,7 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5152,7 +5166,7 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5165,23 +5179,25 @@
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5230,7 +5246,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5242,22 +5258,22 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5265,14 +5281,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5291,17 +5307,17 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5350,7 +5366,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5365,19 +5381,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5385,14 +5401,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5411,18 +5427,18 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5470,7 +5486,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5485,16 +5501,16 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5505,46 +5521,44 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>252</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5568,11 +5582,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5590,13 +5606,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5605,19 +5621,19 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5625,10 +5641,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5639,31 +5655,31 @@
         <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5688,35 +5704,35 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5725,19 +5741,19 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5745,14 +5761,12 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5761,7 +5775,7 @@
         <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>94</v>
@@ -5773,19 +5787,19 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5813,28 +5827,26 @@
         <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5858,10 +5870,10 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5869,24 +5881,26 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
@@ -5895,16 +5909,20 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>266</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>108</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5928,13 +5946,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5952,19 +5970,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5976,10 +5994,10 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5987,21 +6005,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -6013,17 +6031,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6060,31 +6076,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6107,46 +6123,44 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>116</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6182,19 +6196,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>121</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6206,7 +6220,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6215,10 +6229,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6229,10 +6243,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6240,31 +6254,35 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6312,19 +6330,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>110</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6333,10 +6351,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>111</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6347,21 +6365,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6373,17 +6391,15 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6420,31 +6436,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6467,52 +6483,50 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6542,31 +6556,31 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>121</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6575,10 +6589,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>299</v>
+        <v>111</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6589,10 +6603,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6600,13 +6614,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6615,24 +6629,26 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6674,7 +6690,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6695,10 +6711,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6709,10 +6725,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6720,13 +6736,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6735,24 +6751,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6794,7 +6810,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6815,10 +6831,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6829,10 +6845,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6840,13 +6856,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6855,24 +6871,24 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6914,7 +6930,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6935,10 +6951,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6949,10 +6965,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6975,19 +6991,17 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7036,7 +7050,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7057,10 +7071,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7071,10 +7085,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7097,19 +7111,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7158,7 +7172,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7179,10 +7193,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7193,24 +7207,24 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -7219,19 +7233,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7256,13 +7270,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7280,10 +7294,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -7295,62 +7309,66 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>266</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>108</v>
+        <v>351</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7374,13 +7392,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7398,10 +7416,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>110</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -7410,44 +7428,44 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>111</v>
+        <v>360</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7459,17 +7477,15 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7506,31 +7522,31 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7553,18 +7569,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>81</v>
@@ -7576,23 +7592,21 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>280</v>
+        <v>116</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7628,9 +7642,11 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7638,7 +7654,7 @@
         <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>283</v>
+        <v>121</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7650,7 +7666,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7659,10 +7675,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7673,14 +7689,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7689,7 +7703,7 @@
         <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7704,16 +7718,16 @@
         <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7750,19 +7764,17 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7783,10 +7795,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7797,18 +7809,20 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="C45" s="2"/>
+      <c r="C45" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
@@ -7820,19 +7834,23 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7880,19 +7898,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>110</v>
+        <v>288</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7901,10 +7919,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>111</v>
+        <v>290</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7915,21 +7933,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7941,17 +7959,15 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7988,31 +8004,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8035,21 +8051,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8058,29 +8074,27 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8110,31 +8124,31 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>297</v>
+        <v>121</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8143,10 +8157,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>299</v>
+        <v>111</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8157,10 +8171,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8168,7 +8182,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8183,24 +8197,26 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8242,7 +8258,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8263,10 +8279,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8277,10 +8293,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8288,7 +8304,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8303,24 +8319,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8362,7 +8378,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8383,10 +8399,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8397,10 +8413,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8408,7 +8424,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8423,24 +8439,24 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8482,7 +8498,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8503,10 +8519,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8517,10 +8533,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8543,19 +8559,17 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8604,7 +8618,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8625,10 +8639,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8639,10 +8653,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8665,19 +8679,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>332</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8726,7 +8740,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8747,10 +8761,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8761,10 +8775,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8772,13 +8786,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8787,19 +8801,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>382</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>383</v>
+        <v>342</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>386</v>
+        <v>345</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8848,7 +8862,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8863,19 +8877,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>388</v>
+        <v>347</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8883,10 +8897,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8894,13 +8908,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8909,18 +8923,20 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8968,13 +8984,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8983,19 +8999,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9003,21 +9019,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9029,20 +9045,18 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>403</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9090,13 +9104,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9105,19 +9119,19 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>405</v>
+        <v>359</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9125,24 +9139,24 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9151,19 +9165,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9212,7 +9226,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9221,25 +9235,25 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>416</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9247,24 +9261,24 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9273,18 +9287,20 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>129</v>
+        <v>415</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9332,7 +9348,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9341,25 +9357,25 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>421</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9367,10 +9383,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9381,7 +9397,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9393,18 +9409,18 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L58" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9452,13 +9468,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9467,19 +9483,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9487,10 +9503,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9501,10 +9517,10 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9513,19 +9529,17 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9562,59 +9576,59 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9635,19 +9649,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9657,7 +9671,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9684,19 +9698,17 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9705,7 +9717,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9714,29 +9726,31 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9748,25 +9762,29 @@
         <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>107</v>
+        <v>443</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9775,7 +9793,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9814,7 +9832,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>110</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9823,47 +9841,47 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>111</v>
+        <v>452</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9875,17 +9893,15 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9922,31 +9938,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9969,46 +9985,44 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>458</v>
+        <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>459</v>
+        <v>115</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>460</v>
+        <v>116</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10044,31 +10058,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>463</v>
+        <v>121</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10077,10 +10091,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>465</v>
+        <v>111</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10091,10 +10105,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10102,83 +10116,83 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>173</v>
+        <v>463</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q64" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="R64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10199,10 +10213,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10213,10 +10227,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10224,37 +10238,39 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10274,13 +10290,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10298,7 +10314,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10319,10 +10335,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10333,10 +10349,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10359,24 +10375,24 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10418,7 +10434,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10427,7 +10443,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10439,10 +10455,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10453,10 +10469,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10479,26 +10495,24 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10516,13 +10530,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10540,7 +10554,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10549,7 +10563,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10561,10 +10575,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10575,10 +10589,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10586,7 +10600,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>93</v>
@@ -10598,22 +10612,22 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10638,13 +10652,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>155</v>
+        <v>258</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10662,7 +10676,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10671,7 +10685,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10683,10 +10697,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>196</v>
+        <v>488</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10697,10 +10711,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10714,7 +10728,7 @@
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10723,16 +10737,20 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>266</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>108</v>
+        <v>509</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10756,13 +10774,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10780,7 +10798,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>508</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10789,10 +10807,10 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10801,10 +10819,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>111</v>
+        <v>516</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10815,21 +10833,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10841,17 +10859,15 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10888,31 +10904,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10935,14 +10951,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10958,23 +10974,21 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>280</v>
+        <v>116</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11010,19 +11024,19 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>283</v>
+        <v>121</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11034,7 +11048,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11043,10 +11057,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11057,10 +11071,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11071,7 +11085,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11080,19 +11094,23 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11140,19 +11158,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>110</v>
+        <v>288</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11161,10 +11179,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>111</v>
+        <v>290</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11175,21 +11193,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11201,17 +11219,15 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11248,31 +11264,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11295,21 +11311,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11318,23 +11334,21 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11370,31 +11384,31 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>297</v>
+        <v>121</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11403,10 +11417,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>299</v>
+        <v>111</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11417,10 +11431,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11428,7 +11442,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11443,18 +11457,20 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11502,7 +11518,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11523,10 +11539,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11537,10 +11553,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11548,7 +11564,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11563,18 +11579,18 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11622,7 +11638,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11643,10 +11659,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11657,10 +11673,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11668,7 +11684,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>93</v>
@@ -11683,17 +11699,17 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11742,7 +11758,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11763,10 +11779,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11777,10 +11793,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11803,19 +11819,17 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11864,7 +11878,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11885,10 +11899,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11899,10 +11913,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11925,19 +11939,19 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>107</v>
+        <v>332</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11986,7 +12000,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12007,10 +12021,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12021,21 +12035,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -12044,22 +12058,22 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>525</v>
+        <v>342</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>526</v>
+        <v>343</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>527</v>
+        <v>344</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>528</v>
+        <v>345</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12084,11 +12098,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12106,13 +12122,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>523</v>
+        <v>346</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -12124,31 +12140,31 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>531</v>
+        <v>347</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>532</v>
+        <v>348</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12167,19 +12183,19 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>535</v>
+        <v>266</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12204,13 +12220,11 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12228,7 +12242,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12246,27 +12260,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12277,7 +12291,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12289,18 +12303,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>261</v>
+        <v>540</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="N82" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12324,13 +12340,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12348,13 +12364,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12366,27 +12382,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12400,7 +12416,7 @@
         <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12409,20 +12425,18 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12446,11 +12460,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12468,7 +12484,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12486,27 +12502,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12520,7 +12536,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12529,18 +12545,20 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O84" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L84" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12564,13 +12582,11 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12588,7 +12604,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12606,27 +12622,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12640,7 +12656,7 @@
         <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
@@ -12649,16 +12665,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12708,7 +12724,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12726,27 +12742,27 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12757,10 +12773,10 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>82</v>
@@ -12769,20 +12785,18 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12830,45 +12844,45 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>584</v>
+        <v>105</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12879,7 +12893,7 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12891,16 +12905,20 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>584</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>108</v>
+        <v>585</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12948,19 +12966,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>583</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12969,10 +12987,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>111</v>
+        <v>591</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12983,21 +13001,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13009,17 +13027,15 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13068,19 +13084,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13103,14 +13119,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>590</v>
+        <v>113</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13123,26 +13139,24 @@
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>591</v>
+        <v>115</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>592</v>
+        <v>116</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O89" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13190,7 +13204,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>593</v>
+        <v>121</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13214,7 +13228,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13232,26 +13246,26 @@
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>595</v>
+        <v>114</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>596</v>
@@ -13259,8 +13273,12 @@
       <c r="M90" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+      <c r="N90" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13308,19 +13326,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13329,10 +13347,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>600</v>
+        <v>196</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13343,10 +13361,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13369,13 +13387,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13426,7 +13444,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13435,7 +13453,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13447,10 +13465,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13461,10 +13479,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13487,20 +13505,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>261</v>
+        <v>600</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N92" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="O92" t="s" s="2">
-        <v>609</v>
-      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13524,13 +13538,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13548,7 +13562,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13557,7 +13571,7 @@
         <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>105</v>
@@ -13566,13 +13580,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>612</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>532</v>
+        <v>609</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13583,10 +13597,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13597,7 +13611,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13609,19 +13623,19 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13646,13 +13660,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13670,13 +13684,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13688,13 +13702,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13705,10 +13719,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13719,7 +13733,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13731,17 +13745,19 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13766,13 +13782,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13790,13 +13806,13 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13808,13 +13824,13 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>626</v>
+        <v>537</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13825,10 +13841,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13851,7 +13867,7 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>627</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>628</v>
@@ -13860,7 +13876,9 @@
         <v>629</v>
       </c>
       <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13908,7 +13926,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13929,10 +13947,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13943,10 +13961,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13957,7 +13975,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13966,10 +13984,10 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>632</v>
+        <v>107</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>633</v>
@@ -13977,9 +13995,7 @@
       <c r="M96" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N96" t="s" s="2">
-        <v>635</v>
-      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14028,13 +14044,13 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
@@ -14049,10 +14065,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14063,10 +14079,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14089,16 +14105,16 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14148,7 +14164,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14169,10 +14185,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14183,10 +14199,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14200,7 +14216,7 @@
         <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
@@ -14209,20 +14225,18 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>645</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O98" t="s" s="2">
         <v>647</v>
       </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14270,7 +14284,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14282,19 +14296,19 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14305,10 +14319,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14319,28 +14333,32 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>107</v>
+        <v>584</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>108</v>
+        <v>650</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14388,19 +14406,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>110</v>
+        <v>649</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14409,10 +14427,10 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>111</v>
+        <v>655</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14423,21 +14441,21 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14449,17 +14467,15 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14508,19 +14524,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14543,14 +14559,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>590</v>
+        <v>113</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14563,26 +14579,24 @@
         <v>82</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>591</v>
+        <v>115</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>592</v>
+        <v>116</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O101" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14630,7 +14644,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>593</v>
+        <v>121</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14654,7 +14668,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14665,45 +14679,45 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I102" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>261</v>
+        <v>114</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>655</v>
+        <v>596</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>656</v>
+        <v>597</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>657</v>
+        <v>117</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>658</v>
+        <v>224</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14728,13 +14742,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14752,34 +14766,34 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>654</v>
+        <v>598</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>659</v>
+        <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>355</v>
+        <v>196</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
@@ -14787,10 +14801,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14798,7 +14812,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>93</v>
@@ -14813,19 +14827,19 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14853,10 +14867,10 @@
         <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>665</v>
+        <v>355</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>666</v>
+        <v>356</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14874,16 +14888,16 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>667</v>
+        <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14892,27 +14906,27 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>446</v>
+        <v>359</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14932,22 +14946,22 @@
         <v>82</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>261</v>
+        <v>666</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>507</v>
+        <v>446</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14975,10 +14989,10 @@
         <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>508</v>
+        <v>670</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>509</v>
+        <v>671</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14996,7 +15010,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15005,7 +15019,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15014,19 +15028,19 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>673</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>196</v>
+        <v>451</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>511</v>
+        <v>452</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
     </row>
     <row r="105" hidden="true">
@@ -15038,17 +15052,17 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>82</v>
@@ -15057,19 +15071,19 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>525</v>
+        <v>675</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>526</v>
+        <v>676</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>527</v>
+        <v>677</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15097,10 +15111,10 @@
         <v>155</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>675</v>
+        <v>513</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15124,10 +15138,10 @@
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>105</v>
@@ -15136,31 +15150,31 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>531</v>
+        <v>196</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15179,19 +15193,19 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>677</v>
+        <v>530</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>678</v>
+        <v>531</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>582</v>
+        <v>532</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>583</v>
+        <v>533</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15216,13 +15230,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>82</v>
+        <v>680</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15240,7 +15254,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15258,23 +15272,145 @@
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP106">
+  <autoFilter ref="A1:AP107">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15284,7 +15420,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI106">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1367,7 +1367,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2482,7 +2482,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
